--- a/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/lda_axes_summary.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/lda_axes_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,22 +452,9 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.23999999999999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>LD2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="C3" t="n">
         <v>100</v>
       </c>
     </row>
